--- a/artfynd/A 61378-2025 artfynd.xlsx
+++ b/artfynd/A 61378-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130803158</v>
       </c>
       <c r="B2" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130803162</v>
       </c>
       <c r="B3" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>130803159</v>
       </c>
       <c r="B4" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>130803161</v>
       </c>
       <c r="B5" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>130803160</v>
       </c>
       <c r="B6" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 61378-2025 artfynd.xlsx
+++ b/artfynd/A 61378-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130803158</v>
       </c>
       <c r="B2" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>130803162</v>
       </c>
       <c r="B3" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>130803159</v>
       </c>
       <c r="B4" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>130803161</v>
       </c>
       <c r="B5" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>130803160</v>
       </c>
       <c r="B6" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 61378-2025 artfynd.xlsx
+++ b/artfynd/A 61378-2025 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>130803158</v>
       </c>
       <c r="B2" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -777,14 +777,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130803162</v>
+        <v>130803159</v>
       </c>
       <c r="B3" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>463485</v>
+        <v>463597</v>
       </c>
       <c r="R3" t="n">
-        <v>7071163</v>
+        <v>7071378</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,14 +879,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130803159</v>
+        <v>130803160</v>
       </c>
       <c r="B4" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463597</v>
+        <v>463788</v>
       </c>
       <c r="R4" t="n">
-        <v>7071378</v>
+        <v>7071275</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,11 +984,11 @@
         <v>130803161</v>
       </c>
       <c r="B5" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1083,14 +1083,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130803160</v>
+        <v>130803162</v>
       </c>
       <c r="B6" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463788</v>
+        <v>463485</v>
       </c>
       <c r="R6" t="n">
-        <v>7071275</v>
+        <v>7071163</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
